--- a/Data/collapsed database manual cases/chihuahua_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/chihuahua_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7158CB75-F0F3-E441-9B60-5876AAF7FBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE368181-773A-114C-A65C-7760F74A9D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22040" yWindow="7560" windowWidth="22040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4539" uniqueCount="728">
   <si>
     <t>uniqueid</t>
   </si>
@@ -2204,6 +2204,9 @@
   </si>
   <si>
     <t>DANIEL AARON SILVA FIGUEROA</t>
+  </si>
+  <si>
+    <t>SERGIO LUIS OLVERA GALLEGOS</t>
   </si>
 </sst>
 </file>
@@ -2603,7 +2606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S505"/>
+  <dimension ref="A1:S506"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -22623,7 +22626,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>8015</v>
       </c>
@@ -22644,7 +22647,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>8064</v>
       </c>
@@ -22665,7 +22668,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>8030</v>
       </c>
@@ -22686,7 +22689,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>8046</v>
       </c>
@@ -22707,7 +22710,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>8023</v>
       </c>
@@ -22728,7 +22731,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>8019</v>
       </c>
@@ -22749,7 +22752,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>8031</v>
       </c>
@@ -22770,7 +22773,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>8037</v>
       </c>
@@ -22791,7 +22794,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>8065</v>
       </c>
@@ -22807,6 +22810,29 @@
       <c r="G505" s="6"/>
       <c r="H505" s="7" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A506">
+        <v>8016</v>
+      </c>
+      <c r="B506">
+        <v>2024</v>
+      </c>
+      <c r="E506" t="s">
+        <v>200</v>
+      </c>
+      <c r="F506" t="s">
+        <v>727</v>
+      </c>
+      <c r="H506" t="s">
+        <v>200</v>
+      </c>
+      <c r="J506" t="s">
+        <v>200</v>
+      </c>
+      <c r="K506" t="s">
+        <v>727</v>
       </c>
     </row>
   </sheetData>
